--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/AE/Monthly/monthly_combined_bootstrap_summary_encounters_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/AE/Monthly/monthly_combined_bootstrap_summary_encounters_SOURCE.xlsx
@@ -426,34 +426,34 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>7.466</v>
+        <v>0.609</v>
       </c>
       <c r="D2">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0.135</v>
+        <v>0.004</v>
       </c>
       <c r="F2">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>7.208</v>
+        <v>0.602</v>
       </c>
       <c r="H2">
-        <v>7.737</v>
+        <v>0.619</v>
       </c>
       <c r="I2">
-        <v>7.203</v>
+        <v>0.602</v>
       </c>
       <c r="J2">
-        <v>7.738</v>
+        <v>0.618</v>
       </c>
       <c r="K2">
-        <v>7.2</v>
+        <v>0.601</v>
       </c>
       <c r="L2">
-        <v>7.735</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="3">
@@ -466,34 +466,34 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>0.861</v>
+        <v>0.067</v>
       </c>
       <c r="D3">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0.046</v>
+        <v>0.002</v>
       </c>
       <c r="F3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>0.77</v>
+        <v>0.063</v>
       </c>
       <c r="H3">
-        <v>0.95</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="I3">
-        <v>0.762</v>
+        <v>0.063</v>
       </c>
       <c r="J3">
-        <v>0.947</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K3">
-        <v>0.774</v>
+        <v>0.063</v>
       </c>
       <c r="L3">
-        <v>0.958</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -506,34 +506,34 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>0.742</v>
+        <v>0.054</v>
       </c>
       <c r="D4">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0.041</v>
+        <v>0.002</v>
       </c>
       <c r="F4">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>0.655</v>
+        <v>0.05</v>
       </c>
       <c r="H4">
-        <v>0.8179999999999999</v>
+        <v>0.058</v>
       </c>
       <c r="I4">
-        <v>0.647</v>
+        <v>0.05</v>
       </c>
       <c r="J4">
-        <v>0.8120000000000001</v>
+        <v>0.057</v>
       </c>
       <c r="K4">
-        <v>0.667</v>
+        <v>0.051</v>
       </c>
       <c r="L4">
-        <v>0.832</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="5">
@@ -546,34 +546,34 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>0.598</v>
+        <v>0.045</v>
       </c>
       <c r="D5">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0.036</v>
+        <v>0.002</v>
       </c>
       <c r="F5">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>0.526</v>
+        <v>0.042</v>
       </c>
       <c r="H5">
-        <v>0.669</v>
+        <v>0.048</v>
       </c>
       <c r="I5">
-        <v>0.521</v>
+        <v>0.042</v>
       </c>
       <c r="J5">
-        <v>0.666</v>
+        <v>0.048</v>
       </c>
       <c r="K5">
-        <v>0.529</v>
+        <v>0.042</v>
       </c>
       <c r="L5">
-        <v>0.673</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="6">
@@ -586,34 +586,34 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>0.519</v>
+        <v>0.042</v>
       </c>
       <c r="D6">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0.04</v>
+        <v>0.002</v>
       </c>
       <c r="F6">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>0.436</v>
+        <v>0.038</v>
       </c>
       <c r="H6">
-        <v>0.593</v>
+        <v>0.045</v>
       </c>
       <c r="I6">
-        <v>0.432</v>
+        <v>0.038</v>
       </c>
       <c r="J6">
-        <v>0.589</v>
+        <v>0.045</v>
       </c>
       <c r="K6">
-        <v>0.444</v>
+        <v>0.038</v>
       </c>
       <c r="L6">
-        <v>0.601</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="7">
@@ -626,34 +626,34 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>0.593</v>
+        <v>0.044</v>
       </c>
       <c r="D7">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0.043</v>
+        <v>0.002</v>
       </c>
       <c r="F7">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>0.504</v>
+        <v>0.04</v>
       </c>
       <c r="H7">
-        <v>0.672</v>
+        <v>0.048</v>
       </c>
       <c r="I7">
-        <v>0.501</v>
+        <v>0.04</v>
       </c>
       <c r="J7">
-        <v>0.673</v>
+        <v>0.048</v>
       </c>
       <c r="K7">
-        <v>0.507</v>
+        <v>0.04</v>
       </c>
       <c r="L7">
-        <v>0.679</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="8">
@@ -666,34 +666,34 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>0.599</v>
+        <v>0.041</v>
       </c>
       <c r="D8">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E8">
+        <v>0.002</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0.038</v>
+      </c>
+      <c r="H8">
         <v>0.045</v>
       </c>
-      <c r="F8">
-        <v>0.001</v>
-      </c>
-      <c r="G8">
-        <v>0.513</v>
-      </c>
-      <c r="H8">
-        <v>0.6889999999999999</v>
-      </c>
       <c r="I8">
-        <v>0.508</v>
+        <v>0.037</v>
       </c>
       <c r="J8">
-        <v>0.6830000000000001</v>
+        <v>0.045</v>
       </c>
       <c r="K8">
-        <v>0.517</v>
+        <v>0.038</v>
       </c>
       <c r="L8">
-        <v>0.6919999999999999</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="9">
@@ -706,34 +706,34 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>0.553</v>
+        <v>0.04</v>
       </c>
       <c r="D9">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0.057</v>
+        <v>0.002</v>
       </c>
       <c r="F9">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>0.44</v>
+        <v>0.037</v>
       </c>
       <c r="H9">
-        <v>0.664</v>
+        <v>0.043</v>
       </c>
       <c r="I9">
-        <v>0.43</v>
+        <v>0.037</v>
       </c>
       <c r="J9">
-        <v>0.658</v>
+        <v>0.043</v>
       </c>
       <c r="K9">
-        <v>0.447</v>
+        <v>0.036</v>
       </c>
       <c r="L9">
-        <v>0.675</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="10">
@@ -746,34 +746,34 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>0.659</v>
+        <v>0.043</v>
       </c>
       <c r="D10">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>0.049</v>
+        <v>0.002</v>
       </c>
       <c r="F10">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>0.5629999999999999</v>
+        <v>0.04</v>
       </c>
       <c r="H10">
-        <v>0.756</v>
+        <v>0.047</v>
       </c>
       <c r="I10">
-        <v>0.553</v>
+        <v>0.04</v>
       </c>
       <c r="J10">
-        <v>0.752</v>
+        <v>0.047</v>
       </c>
       <c r="K10">
-        <v>0.5659999999999999</v>
+        <v>0.04</v>
       </c>
       <c r="L10">
-        <v>0.765</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="11">
@@ -786,34 +786,34 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>0.575</v>
+        <v>0.04</v>
       </c>
       <c r="D11">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.048</v>
+        <v>0.002</v>
       </c>
       <c r="F11">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>0.478</v>
+        <v>0.036</v>
       </c>
       <c r="H11">
-        <v>0.664</v>
+        <v>0.043</v>
       </c>
       <c r="I11">
-        <v>0.472</v>
+        <v>0.036</v>
       </c>
       <c r="J11">
-        <v>0.66</v>
+        <v>0.043</v>
       </c>
       <c r="K11">
-        <v>0.486</v>
+        <v>0.036</v>
       </c>
       <c r="L11">
-        <v>0.674</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="12">
@@ -826,34 +826,34 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>0.587</v>
+        <v>0.041</v>
       </c>
       <c r="D12">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E12">
+        <v>0.002</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0.037</v>
+      </c>
+      <c r="H12">
         <v>0.045</v>
       </c>
-      <c r="F12">
-        <v>0.001</v>
-      </c>
-      <c r="G12">
-        <v>0.496</v>
-      </c>
-      <c r="H12">
-        <v>0.671</v>
-      </c>
       <c r="I12">
-        <v>0.495</v>
+        <v>0.037</v>
       </c>
       <c r="J12">
-        <v>0.669</v>
+        <v>0.045</v>
       </c>
       <c r="K12">
-        <v>0.501</v>
+        <v>0.037</v>
       </c>
       <c r="L12">
-        <v>0.676</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="13">
@@ -866,34 +866,34 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>0.638</v>
+        <v>0.041</v>
       </c>
       <c r="D13">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>0.049</v>
+        <v>0.002</v>
       </c>
       <c r="F13">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>0.544</v>
+        <v>0.037</v>
       </c>
       <c r="H13">
-        <v>0.734</v>
+        <v>0.044</v>
       </c>
       <c r="I13">
-        <v>0.54</v>
+        <v>0.037</v>
       </c>
       <c r="J13">
-        <v>0.732</v>
+        <v>0.044</v>
       </c>
       <c r="K13">
-        <v>0.545</v>
+        <v>0.037</v>
       </c>
       <c r="L13">
-        <v>0.737</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="14">
@@ -906,34 +906,34 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>0.522</v>
+        <v>0.037</v>
       </c>
       <c r="D14">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>0.044</v>
+        <v>0.002</v>
       </c>
       <c r="F14">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>0.436</v>
+        <v>0.033</v>
       </c>
       <c r="H14">
-        <v>0.61</v>
+        <v>0.041</v>
       </c>
       <c r="I14">
-        <v>0.43</v>
+        <v>0.033</v>
       </c>
       <c r="J14">
-        <v>0.605</v>
+        <v>0.04</v>
       </c>
       <c r="K14">
-        <v>0.44</v>
+        <v>0.033</v>
       </c>
       <c r="L14">
-        <v>0.614</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="15">
@@ -946,34 +946,34 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>0.588</v>
+        <v>0.04</v>
       </c>
       <c r="D15">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>0.059</v>
+        <v>0.002</v>
       </c>
       <c r="F15">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>0.474</v>
+        <v>0.036</v>
       </c>
       <c r="H15">
-        <v>0.706</v>
+        <v>0.043</v>
       </c>
       <c r="I15">
-        <v>0.472</v>
+        <v>0.036</v>
       </c>
       <c r="J15">
-        <v>0.699</v>
+        <v>0.043</v>
       </c>
       <c r="K15">
-        <v>0.479</v>
+        <v>0.036</v>
       </c>
       <c r="L15">
-        <v>0.706</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="16">
@@ -986,34 +986,34 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>0.524</v>
+        <v>0.038</v>
       </c>
       <c r="D16">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>0.055</v>
+        <v>0.002</v>
       </c>
       <c r="F16">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>0.418</v>
+        <v>0.034</v>
       </c>
       <c r="H16">
-        <v>0.635</v>
+        <v>0.041</v>
       </c>
       <c r="I16">
-        <v>0.409</v>
+        <v>0.034</v>
       </c>
       <c r="J16">
-        <v>0.628</v>
+        <v>0.041</v>
       </c>
       <c r="K16">
-        <v>0.423</v>
+        <v>0.034</v>
       </c>
       <c r="L16">
-        <v>0.641</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="17">
@@ -1026,34 +1026,34 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>0.5600000000000001</v>
+        <v>0.041</v>
       </c>
       <c r="D17">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>0.046</v>
+        <v>0.002</v>
       </c>
       <c r="F17">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>0.47</v>
+        <v>0.037</v>
       </c>
       <c r="H17">
-        <v>0.65</v>
+        <v>0.045</v>
       </c>
       <c r="I17">
-        <v>0.468</v>
+        <v>0.037</v>
       </c>
       <c r="J17">
-        <v>0.647</v>
+        <v>0.045</v>
       </c>
       <c r="K17">
-        <v>0.473</v>
+        <v>0.037</v>
       </c>
       <c r="L17">
-        <v>0.652</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="18">
@@ -1066,34 +1066,34 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>0.491</v>
+        <v>0.036</v>
       </c>
       <c r="D18">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>0.042</v>
+        <v>0.002</v>
       </c>
       <c r="F18">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>0.411</v>
+        <v>0.032</v>
       </c>
       <c r="H18">
-        <v>0.575</v>
+        <v>0.04</v>
       </c>
       <c r="I18">
-        <v>0.406</v>
+        <v>0.032</v>
       </c>
       <c r="J18">
-        <v>0.575</v>
+        <v>0.04</v>
       </c>
       <c r="K18">
-        <v>0.409</v>
+        <v>0.032</v>
       </c>
       <c r="L18">
-        <v>0.579</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="19">
@@ -1106,34 +1106,34 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>0.591</v>
+        <v>0.041</v>
       </c>
       <c r="D19">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>0.059</v>
+        <v>0.002</v>
       </c>
       <c r="F19">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>0.472</v>
+        <v>0.037</v>
       </c>
       <c r="H19">
-        <v>0.703</v>
+        <v>0.045</v>
       </c>
       <c r="I19">
-        <v>0.47</v>
+        <v>0.037</v>
       </c>
       <c r="J19">
-        <v>0.6919999999999999</v>
+        <v>0.045</v>
       </c>
       <c r="K19">
-        <v>0.485</v>
+        <v>0.037</v>
       </c>
       <c r="L19">
-        <v>0.707</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="20">
@@ -1146,34 +1146,34 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>0.62</v>
+        <v>0.041</v>
       </c>
       <c r="D20">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>0.057</v>
+        <v>0.002</v>
       </c>
       <c r="F20">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>0.502</v>
+        <v>0.037</v>
       </c>
       <c r="H20">
-        <v>0.725</v>
+        <v>0.045</v>
       </c>
       <c r="I20">
-        <v>0.498</v>
+        <v>0.037</v>
       </c>
       <c r="J20">
-        <v>0.724</v>
+        <v>0.046</v>
       </c>
       <c r="K20">
-        <v>0.51</v>
+        <v>0.037</v>
       </c>
       <c r="L20">
-        <v>0.736</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="21">
@@ -1186,34 +1186,34 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>0.581</v>
+        <v>0.039</v>
       </c>
       <c r="D21">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>0.059</v>
+        <v>0.002</v>
       </c>
       <c r="F21">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>0.463</v>
+        <v>0.034</v>
       </c>
       <c r="H21">
-        <v>0.696</v>
+        <v>0.043</v>
       </c>
       <c r="I21">
-        <v>0.456</v>
+        <v>0.034</v>
       </c>
       <c r="J21">
-        <v>0.695</v>
+        <v>0.043</v>
       </c>
       <c r="K21">
-        <v>0.465</v>
+        <v>0.035</v>
       </c>
       <c r="L21">
-        <v>0.704</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="22">
@@ -1226,34 +1226,34 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>0.626</v>
+        <v>0.041</v>
       </c>
       <c r="D22">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>0.058</v>
+        <v>0.002</v>
       </c>
       <c r="F22">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>0.505</v>
+        <v>0.036</v>
       </c>
       <c r="H22">
-        <v>0.733</v>
+        <v>0.045</v>
       </c>
       <c r="I22">
-        <v>0.502</v>
+        <v>0.036</v>
       </c>
       <c r="J22">
-        <v>0.728</v>
+        <v>0.045</v>
       </c>
       <c r="K22">
-        <v>0.517</v>
+        <v>0.037</v>
       </c>
       <c r="L22">
-        <v>0.743</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="23">
@@ -1266,34 +1266,34 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>0.589</v>
+        <v>0.038</v>
       </c>
       <c r="D23">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>0.054</v>
+        <v>0.002</v>
       </c>
       <c r="F23">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>0.478</v>
+        <v>0.034</v>
       </c>
       <c r="H23">
-        <v>0.6879999999999999</v>
+        <v>0.042</v>
       </c>
       <c r="I23">
-        <v>0.478</v>
+        <v>0.034</v>
       </c>
       <c r="J23">
-        <v>0.6860000000000001</v>
+        <v>0.042</v>
       </c>
       <c r="K23">
-        <v>0.486</v>
+        <v>0.034</v>
       </c>
       <c r="L23">
-        <v>0.694</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="24">
@@ -1306,34 +1306,34 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>0.598</v>
+        <v>0.042</v>
       </c>
       <c r="D24">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>0.058</v>
+        <v>0.002</v>
       </c>
       <c r="F24">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>0.484</v>
+        <v>0.037</v>
       </c>
       <c r="H24">
-        <v>0.713</v>
+        <v>0.047</v>
       </c>
       <c r="I24">
-        <v>0.477</v>
+        <v>0.037</v>
       </c>
       <c r="J24">
-        <v>0.707</v>
+        <v>0.046</v>
       </c>
       <c r="K24">
-        <v>0.489</v>
+        <v>0.037</v>
       </c>
       <c r="L24">
-        <v>0.719</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="25">
@@ -1346,34 +1346,34 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>0.631</v>
+        <v>0.036</v>
       </c>
       <c r="D25">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>0.076</v>
+        <v>0.002</v>
       </c>
       <c r="F25">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>0.493</v>
+        <v>0.031</v>
       </c>
       <c r="H25">
-        <v>0.79</v>
+        <v>0.04</v>
       </c>
       <c r="I25">
-        <v>0.485</v>
+        <v>0.032</v>
       </c>
       <c r="J25">
-        <v>0.781</v>
+        <v>0.04</v>
       </c>
       <c r="K25">
-        <v>0.492</v>
+        <v>0.031</v>
       </c>
       <c r="L25">
-        <v>0.787</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="26">
@@ -1386,34 +1386,34 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>11.043</v>
+        <v>0.902</v>
       </c>
       <c r="D26">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>0.194</v>
+        <v>0.005</v>
       </c>
       <c r="F26">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>10.664</v>
+        <v>0.892</v>
       </c>
       <c r="H26">
-        <v>11.423</v>
+        <v>0.912</v>
       </c>
       <c r="I26">
-        <v>10.661</v>
+        <v>0.892</v>
       </c>
       <c r="J26">
-        <v>11.416</v>
+        <v>0.912</v>
       </c>
       <c r="K26">
-        <v>10.67</v>
+        <v>0.891</v>
       </c>
       <c r="L26">
-        <v>11.425</v>
+        <v>0.911</v>
       </c>
     </row>
     <row r="27">
@@ -1426,34 +1426,34 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>1.273</v>
+        <v>0.099</v>
       </c>
       <c r="D27">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>0.068</v>
+        <v>0.003</v>
       </c>
       <c r="F27">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>1.138</v>
+        <v>0.094</v>
       </c>
       <c r="H27">
-        <v>1.404</v>
+        <v>0.105</v>
       </c>
       <c r="I27">
-        <v>1.133</v>
+        <v>0.094</v>
       </c>
       <c r="J27">
-        <v>1.409</v>
+        <v>0.105</v>
       </c>
       <c r="K27">
-        <v>1.136</v>
+        <v>0.093</v>
       </c>
       <c r="L27">
-        <v>1.412</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="28">
@@ -1466,34 +1466,34 @@
         <v>3</v>
       </c>
       <c r="C28">
-        <v>1.084</v>
+        <v>0.079</v>
       </c>
       <c r="D28">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>0.06</v>
+        <v>0.003</v>
       </c>
       <c r="F28">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>0.972</v>
+        <v>0.074</v>
       </c>
       <c r="H28">
-        <v>1.207</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I28">
-        <v>0.979</v>
+        <v>0.074</v>
       </c>
       <c r="J28">
-        <v>1.205</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K28">
-        <v>0.968</v>
+        <v>0.074</v>
       </c>
       <c r="L28">
-        <v>1.195</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1506,34 +1506,34 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>0.876</v>
+        <v>0.066</v>
       </c>
       <c r="D29">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>0.055</v>
+        <v>0.002</v>
       </c>
       <c r="F29">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>0.77</v>
+        <v>0.062</v>
       </c>
       <c r="H29">
-        <v>0.984</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="I29">
-        <v>0.767</v>
+        <v>0.061</v>
       </c>
       <c r="J29">
-        <v>0.98</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K29">
-        <v>0.773</v>
+        <v>0.061</v>
       </c>
       <c r="L29">
-        <v>0.986</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1546,34 +1546,34 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>0.754</v>
+        <v>0.06</v>
       </c>
       <c r="D30">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>0.057</v>
+        <v>0.002</v>
       </c>
       <c r="F30">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>0.639</v>
+        <v>0.056</v>
       </c>
       <c r="H30">
-        <v>0.861</v>
+        <v>0.065</v>
       </c>
       <c r="I30">
-        <v>0.641</v>
+        <v>0.056</v>
       </c>
       <c r="J30">
-        <v>0.857</v>
+        <v>0.065</v>
       </c>
       <c r="K30">
-        <v>0.647</v>
+        <v>0.056</v>
       </c>
       <c r="L30">
-        <v>0.863</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="31">
@@ -1586,34 +1586,34 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.853</v>
+        <v>0.063</v>
       </c>
       <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
         <v>0.003</v>
       </c>
-      <c r="E31">
-        <v>0.059</v>
-      </c>
       <c r="F31">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>0.743</v>
+        <v>0.058</v>
       </c>
       <c r="H31">
-        <v>0.972</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I31">
-        <v>0.74</v>
+        <v>0.058</v>
       </c>
       <c r="J31">
-        <v>0.97</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K31">
-        <v>0.741</v>
+        <v>0.058</v>
       </c>
       <c r="L31">
-        <v>0.971</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1626,34 +1626,34 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>0.868</v>
+        <v>0.059</v>
       </c>
       <c r="D32">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>0.063</v>
+        <v>0.003</v>
       </c>
       <c r="F32">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>0.746</v>
+        <v>0.055</v>
       </c>
       <c r="H32">
-        <v>0.992</v>
+        <v>0.064</v>
       </c>
       <c r="I32">
-        <v>0.743</v>
+        <v>0.055</v>
       </c>
       <c r="J32">
-        <v>0.989</v>
+        <v>0.064</v>
       </c>
       <c r="K32">
-        <v>0.748</v>
+        <v>0.054</v>
       </c>
       <c r="L32">
-        <v>0.994</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="33">
@@ -1666,34 +1666,34 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>0.797</v>
+        <v>0.058</v>
       </c>
       <c r="D33">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>0.083</v>
+        <v>0.002</v>
       </c>
       <c r="F33">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>0.636</v>
+        <v>0.053</v>
       </c>
       <c r="H33">
-        <v>0.961</v>
+        <v>0.062</v>
       </c>
       <c r="I33">
-        <v>0.63</v>
+        <v>0.053</v>
       </c>
       <c r="J33">
-        <v>0.949</v>
+        <v>0.063</v>
       </c>
       <c r="K33">
-        <v>0.647</v>
+        <v>0.053</v>
       </c>
       <c r="L33">
-        <v>0.966</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="34">
@@ -1706,34 +1706,34 @@
         <v>9</v>
       </c>
       <c r="C34">
-        <v>0.954</v>
+        <v>0.063</v>
       </c>
       <c r="D34">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>0.075</v>
+        <v>0.003</v>
       </c>
       <c r="F34">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>0.801</v>
+        <v>0.057</v>
       </c>
       <c r="H34">
-        <v>1.093</v>
+        <v>0.068</v>
       </c>
       <c r="I34">
-        <v>0.796</v>
+        <v>0.057</v>
       </c>
       <c r="J34">
-        <v>1.083</v>
+        <v>0.068</v>
       </c>
       <c r="K34">
-        <v>0.8179999999999999</v>
+        <v>0.058</v>
       </c>
       <c r="L34">
-        <v>1.105</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="35">
@@ -1746,34 +1746,34 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>0.823</v>
+        <v>0.057</v>
       </c>
       <c r="D35">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>0.068</v>
+        <v>0.003</v>
       </c>
       <c r="F35">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>0.694</v>
+        <v>0.052</v>
       </c>
       <c r="H35">
-        <v>0.961</v>
+        <v>0.062</v>
       </c>
       <c r="I35">
-        <v>0.6870000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="J35">
-        <v>0.946</v>
+        <v>0.062</v>
       </c>
       <c r="K35">
-        <v>0.704</v>
+        <v>0.052</v>
       </c>
       <c r="L35">
-        <v>0.963</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="36">
@@ -1786,34 +1786,34 @@
         <v>11</v>
       </c>
       <c r="C36">
-        <v>0.842</v>
+        <v>0.059</v>
       </c>
       <c r="D36">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="E36">
+        <v>0.003</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0.053</v>
+      </c>
+      <c r="H36">
         <v>0.065</v>
       </c>
-      <c r="F36">
-        <v>0.002</v>
-      </c>
-      <c r="G36">
-        <v>0.715</v>
-      </c>
-      <c r="H36">
-        <v>0.972</v>
-      </c>
       <c r="I36">
-        <v>0.711</v>
+        <v>0.053</v>
       </c>
       <c r="J36">
-        <v>0.963</v>
+        <v>0.065</v>
       </c>
       <c r="K36">
-        <v>0.722</v>
+        <v>0.053</v>
       </c>
       <c r="L36">
-        <v>0.975</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="37">
@@ -1826,34 +1826,34 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>0.92</v>
+        <v>0.059</v>
       </c>
       <c r="D37">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>0.06900000000000001</v>
+        <v>0.003</v>
       </c>
       <c r="F37">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>0.784</v>
+        <v>0.053</v>
       </c>
       <c r="H37">
-        <v>1.055</v>
+        <v>0.064</v>
       </c>
       <c r="I37">
-        <v>0.782</v>
+        <v>0.053</v>
       </c>
       <c r="J37">
-        <v>1.053</v>
+        <v>0.063</v>
       </c>
       <c r="K37">
-        <v>0.786</v>
+        <v>0.054</v>
       </c>
       <c r="L37">
-        <v>1.058</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="38">
@@ -1866,34 +1866,34 @@
         <v>13</v>
       </c>
       <c r="C38">
-        <v>0.76</v>
+        <v>0.053</v>
       </c>
       <c r="D38">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>0.063</v>
+        <v>0.003</v>
       </c>
       <c r="F38">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>0.625</v>
+        <v>0.048</v>
       </c>
       <c r="H38">
-        <v>0.873</v>
+        <v>0.059</v>
       </c>
       <c r="I38">
-        <v>0.62</v>
+        <v>0.048</v>
       </c>
       <c r="J38">
-        <v>0.868</v>
+        <v>0.059</v>
       </c>
       <c r="K38">
-        <v>0.641</v>
+        <v>0.048</v>
       </c>
       <c r="L38">
-        <v>0.889</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="39">
@@ -1906,34 +1906,34 @@
         <v>14</v>
       </c>
       <c r="C39">
-        <v>0.853</v>
+        <v>0.057</v>
       </c>
       <c r="D39">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>0.08799999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="F39">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>0.674</v>
+        <v>0.052</v>
       </c>
       <c r="H39">
-        <v>1.02</v>
+        <v>0.063</v>
       </c>
       <c r="I39">
-        <v>0.671</v>
+        <v>0.052</v>
       </c>
       <c r="J39">
-        <v>1.011</v>
+        <v>0.063</v>
       </c>
       <c r="K39">
-        <v>0.6889999999999999</v>
+        <v>0.052</v>
       </c>
       <c r="L39">
-        <v>1.029</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="40">
@@ -1946,34 +1946,34 @@
         <v>15</v>
       </c>
       <c r="C40">
-        <v>0.759</v>
+        <v>0.054</v>
       </c>
       <c r="D40">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>0.076</v>
+        <v>0.003</v>
       </c>
       <c r="F40">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>0.609</v>
+        <v>0.049</v>
       </c>
       <c r="H40">
-        <v>0.906</v>
+        <v>0.059</v>
       </c>
       <c r="I40">
-        <v>0.589</v>
+        <v>0.049</v>
       </c>
       <c r="J40">
-        <v>0.902</v>
+        <v>0.059</v>
       </c>
       <c r="K40">
-        <v>0.614</v>
+        <v>0.049</v>
       </c>
       <c r="L40">
-        <v>0.927</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="41">
@@ -1986,34 +1986,34 @@
         <v>16</v>
       </c>
       <c r="C41">
-        <v>0.8080000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="D41">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="E41">
+        <v>0.003</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0.054</v>
+      </c>
+      <c r="H41">
         <v>0.065</v>
       </c>
-      <c r="F41">
-        <v>0.002</v>
-      </c>
-      <c r="G41">
-        <v>0.681</v>
-      </c>
-      <c r="H41">
-        <v>0.9350000000000001</v>
-      </c>
       <c r="I41">
-        <v>0.677</v>
+        <v>0.054</v>
       </c>
       <c r="J41">
-        <v>0.9370000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="K41">
-        <v>0.68</v>
+        <v>0.054</v>
       </c>
       <c r="L41">
-        <v>0.9389999999999999</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="42">
@@ -2026,34 +2026,34 @@
         <v>17</v>
       </c>
       <c r="C42">
-        <v>0.711</v>
+        <v>0.052</v>
       </c>
       <c r="D42">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>0.059</v>
+        <v>0.003</v>
       </c>
       <c r="F42">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>0.595</v>
+        <v>0.046</v>
       </c>
       <c r="H42">
-        <v>0.827</v>
+        <v>0.057</v>
       </c>
       <c r="I42">
-        <v>0.589</v>
+        <v>0.046</v>
       </c>
       <c r="J42">
-        <v>0.8179999999999999</v>
+        <v>0.057</v>
       </c>
       <c r="K42">
-        <v>0.604</v>
+        <v>0.047</v>
       </c>
       <c r="L42">
-        <v>0.833</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="43">
@@ -2066,34 +2066,34 @@
         <v>18</v>
       </c>
       <c r="C43">
-        <v>0.853</v>
+        <v>0.059</v>
       </c>
       <c r="D43">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>0.08699999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="F43">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>0.6820000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="H43">
-        <v>1.021</v>
+        <v>0.065</v>
       </c>
       <c r="I43">
-        <v>0.678</v>
+        <v>0.053</v>
       </c>
       <c r="J43">
-        <v>1.009</v>
+        <v>0.065</v>
       </c>
       <c r="K43">
-        <v>0.696</v>
+        <v>0.053</v>
       </c>
       <c r="L43">
-        <v>1.027</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="44">
@@ -2106,34 +2106,34 @@
         <v>19</v>
       </c>
       <c r="C44">
-        <v>0.893</v>
+        <v>0.06</v>
       </c>
       <c r="D44">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>0.083</v>
+        <v>0.003</v>
       </c>
       <c r="F44">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>0.737</v>
+        <v>0.054</v>
       </c>
       <c r="H44">
-        <v>1.062</v>
+        <v>0.066</v>
       </c>
       <c r="I44">
-        <v>0.724</v>
+        <v>0.054</v>
       </c>
       <c r="J44">
-        <v>1.049</v>
+        <v>0.066</v>
       </c>
       <c r="K44">
-        <v>0.743</v>
+        <v>0.054</v>
       </c>
       <c r="L44">
-        <v>1.068</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="45">
@@ -2146,34 +2146,34 @@
         <v>20</v>
       </c>
       <c r="C45">
-        <v>0.839</v>
+        <v>0.056</v>
       </c>
       <c r="D45">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>0.083</v>
+        <v>0.003</v>
       </c>
       <c r="F45">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>0.6830000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H45">
-        <v>1.008</v>
+        <v>0.062</v>
       </c>
       <c r="I45">
-        <v>0.664</v>
+        <v>0.05</v>
       </c>
       <c r="J45">
-        <v>1.006</v>
+        <v>0.062</v>
       </c>
       <c r="K45">
-        <v>0.678</v>
+        <v>0.05</v>
       </c>
       <c r="L45">
-        <v>1.02</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="46">
@@ -2186,34 +2186,34 @@
         <v>21</v>
       </c>
       <c r="C46">
-        <v>0.902</v>
+        <v>0.059</v>
       </c>
       <c r="D46">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>0.08699999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="F46">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>0.739</v>
+        <v>0.053</v>
       </c>
       <c r="H46">
-        <v>1.078</v>
+        <v>0.066</v>
       </c>
       <c r="I46">
-        <v>0.712</v>
+        <v>0.053</v>
       </c>
       <c r="J46">
-        <v>1.067</v>
+        <v>0.066</v>
       </c>
       <c r="K46">
-        <v>0.744</v>
+        <v>0.053</v>
       </c>
       <c r="L46">
-        <v>1.099</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="47">
@@ -2226,34 +2226,34 @@
         <v>22</v>
       </c>
       <c r="C47">
-        <v>0.859</v>
+        <v>0.056</v>
       </c>
       <c r="D47">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>0.078</v>
+        <v>0.003</v>
       </c>
       <c r="F47">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>0.696</v>
+        <v>0.05</v>
       </c>
       <c r="H47">
-        <v>1.002</v>
+        <v>0.061</v>
       </c>
       <c r="I47">
-        <v>0.6929999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="J47">
-        <v>0.999</v>
+        <v>0.061</v>
       </c>
       <c r="K47">
-        <v>0.71</v>
+        <v>0.05</v>
       </c>
       <c r="L47">
-        <v>1.015</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="48">
@@ -2266,34 +2266,34 @@
         <v>23</v>
       </c>
       <c r="C48">
-        <v>0.88</v>
+        <v>0.061</v>
       </c>
       <c r="D48">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>0.081</v>
+        <v>0.003</v>
       </c>
       <c r="F48">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="G48">
-        <v>0.712</v>
+        <v>0.055</v>
       </c>
       <c r="H48">
-        <v>1.03</v>
+        <v>0.068</v>
       </c>
       <c r="I48">
-        <v>0.704</v>
+        <v>0.054</v>
       </c>
       <c r="J48">
-        <v>1.02</v>
+        <v>0.067</v>
       </c>
       <c r="K48">
-        <v>0.731</v>
+        <v>0.055</v>
       </c>
       <c r="L48">
-        <v>1.047</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="49">
@@ -2306,34 +2306,34 @@
         <v>24</v>
       </c>
       <c r="C49">
-        <v>0.9370000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="D49">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>0.117</v>
+        <v>0.003</v>
       </c>
       <c r="F49">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>0.703</v>
+        <v>0.046</v>
       </c>
       <c r="H49">
-        <v>1.16</v>
+        <v>0.058</v>
       </c>
       <c r="I49">
-        <v>0.677</v>
+        <v>0.046</v>
       </c>
       <c r="J49">
-        <v>1.139</v>
+        <v>0.058</v>
       </c>
       <c r="K49">
-        <v>0.729</v>
+        <v>0.046</v>
       </c>
       <c r="L49">
-        <v>1.19</v>
+        <v>0.058</v>
       </c>
     </row>
   </sheetData>
